--- a/data/trans_bre/P16-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 27,73</t>
+          <t>10,65; 27,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 28,34</t>
+          <t>13,06; 29,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 18,75</t>
+          <t>2,47; 18,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 18,2</t>
+          <t>1,6; 18,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 76,98</t>
+          <t>23,21; 78,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 53,82</t>
+          <t>21,49; 56,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 34,45</t>
+          <t>3,92; 33,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 31,23</t>
+          <t>2,45; 31,92</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 26,37</t>
+          <t>13,81; 26,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,1; 27,06</t>
+          <t>13,98; 26,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 24,49</t>
+          <t>12,76; 24,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 22,33</t>
+          <t>7,35; 22,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,11; 76,01</t>
+          <t>32,98; 77,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 57,32</t>
+          <t>25,71; 56,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,36; 54,34</t>
+          <t>25,09; 55,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 49,52</t>
+          <t>13,62; 49,71</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,16; 32,72</t>
+          <t>18,05; 32,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,32; 29,16</t>
+          <t>14,3; 29,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 22,69</t>
+          <t>8,14; 23,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 18,03</t>
+          <t>2,83; 17,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,18; 101,96</t>
+          <t>45,16; 107,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,47; 59,49</t>
+          <t>24,09; 58,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 49,37</t>
+          <t>14,93; 49,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 33,54</t>
+          <t>5,28; 33,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 25,18</t>
+          <t>10,61; 24,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 32,14</t>
+          <t>19,13; 32,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 20,43</t>
+          <t>7,04; 20,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 22,69</t>
+          <t>-6,67; 23,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,56; 70,82</t>
+          <t>22,8; 67,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,32; 72,82</t>
+          <t>35,78; 74,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 35,93</t>
+          <t>10,75; 35,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 42,69</t>
+          <t>-11,25; 45,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 25,2</t>
+          <t>5,82; 25,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 36,76</t>
+          <t>18,65; 35,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,67; 30,43</t>
+          <t>12,3; 30,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 23,45</t>
+          <t>8,11; 23,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 61,2</t>
+          <t>11,37; 60,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,02; 78,79</t>
+          <t>31,58; 76,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 80,17</t>
+          <t>25,46; 81,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,77; 54,93</t>
+          <t>14,91; 54,9</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,47; 32,76</t>
+          <t>16,2; 31,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,65; 26,91</t>
+          <t>11,26; 26,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,52; 25,6</t>
+          <t>8,8; 26,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 14,27</t>
+          <t>-1,27; 13,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,77; 92,46</t>
+          <t>36,28; 90,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,54; 50,14</t>
+          <t>18,01; 49,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 62,14</t>
+          <t>16,67; 62,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 26,81</t>
+          <t>-1,95; 26,15</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 22,83</t>
+          <t>10,98; 21,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 21,29</t>
+          <t>10,05; 21,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 16,99</t>
+          <t>5,7; 16,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 31,0</t>
+          <t>6,11; 30,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,91; 63,75</t>
+          <t>25,93; 61,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,59; 44,29</t>
+          <t>18,19; 42,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,55; 40,29</t>
+          <t>11,32; 39,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 54,37</t>
+          <t>9,35; 53,67</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 17,74</t>
+          <t>6,66; 16,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,02; 22,26</t>
+          <t>12,34; 22,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,75; 20,41</t>
+          <t>10,6; 20,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,52; 40,42</t>
+          <t>11,43; 40,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,2; 42,28</t>
+          <t>14,39; 40,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,68; 57,1</t>
+          <t>27,59; 59,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,92; 44,83</t>
+          <t>21,1; 45,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,9; 316,65</t>
+          <t>28,83; 285,23</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,7; 20,48</t>
+          <t>15,68; 20,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,37</t>
+          <t>17,36; 22,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,55</t>
+          <t>12,82; 17,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 29,75</t>
+          <t>11,03; 29,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,43; 52,27</t>
+          <t>37,4; 52,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,9; 45,53</t>
+          <t>33,5; 45,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,97; 36,07</t>
+          <t>25,34; 35,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,34; 75,12</t>
+          <t>20,5; 75,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 27,92</t>
+          <t>10,92; 28,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 29,14</t>
+          <t>12,72; 28,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 18,19</t>
+          <t>1,94; 18,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 18,55</t>
+          <t>2,55; 16,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,21; 78,67</t>
+          <t>25,12; 81,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,49; 56,76</t>
+          <t>20,78; 55,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 33,52</t>
+          <t>2,97; 34,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 31,92</t>
+          <t>3,8; 27,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>13,78</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,81; 26,59</t>
+          <t>14,07; 26,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,98; 26,75</t>
+          <t>14,82; 27,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 24,58</t>
+          <t>12,86; 24,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 22,14</t>
+          <t>7,51; 20,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,98; 77,37</t>
+          <t>34,0; 75,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 56,54</t>
+          <t>26,98; 57,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,09; 55,66</t>
+          <t>25,1; 55,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 49,71</t>
+          <t>13,9; 46,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,99</t>
+          <t>10,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 32,84</t>
+          <t>17,37; 33,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 29,27</t>
+          <t>15,72; 29,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 23,09</t>
+          <t>7,82; 22,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 17,79</t>
+          <t>4,05; 17,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,16; 107,97</t>
+          <t>42,27; 105,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,09; 58,48</t>
+          <t>27,15; 60,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,93; 49,24</t>
+          <t>14,47; 48,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 33,0</t>
+          <t>6,29; 33,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>10,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 24,93</t>
+          <t>10,42; 24,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 32,6</t>
+          <t>18,36; 32,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 20,07</t>
+          <t>6,81; 20,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 23,38</t>
+          <t>2,19; 19,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 67,28</t>
+          <t>23,7; 68,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,78; 74,91</t>
+          <t>34,33; 72,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 35,11</t>
+          <t>10,2; 35,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 45,75</t>
+          <t>3,64; 41,17</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,13</t>
+          <t>16,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 25,64</t>
+          <t>6,78; 25,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,65; 35,95</t>
+          <t>18,9; 36,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,3; 30,71</t>
+          <t>11,05; 30,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 23,73</t>
+          <t>9,06; 24,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 60,83</t>
+          <t>12,78; 61,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,58; 76,01</t>
+          <t>32,48; 76,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,46; 81,71</t>
+          <t>22,96; 80,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 54,9</t>
+          <t>17,89; 62,08</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,2; 31,99</t>
+          <t>15,16; 32,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 26,49</t>
+          <t>11,71; 27,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,8; 26,61</t>
+          <t>8,24; 25,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 13,87</t>
+          <t>-0,4; 14,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,28; 90,68</t>
+          <t>33,69; 90,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,01; 49,17</t>
+          <t>18,21; 50,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,67; 62,97</t>
+          <t>15,48; 62,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 26,15</t>
+          <t>-0,47; 27,0</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,27</t>
+          <t>8,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 21,92</t>
+          <t>11,2; 22,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 21,08</t>
+          <t>9,34; 20,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 16,8</t>
+          <t>5,78; 16,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 30,33</t>
+          <t>2,49; 13,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,93; 61,57</t>
+          <t>27,74; 62,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,19; 42,89</t>
+          <t>16,68; 41,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,32; 39,74</t>
+          <t>12,19; 39,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 53,67</t>
+          <t>3,89; 24,23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,16</t>
+          <t>13,06</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 16,93</t>
+          <t>7,21; 17,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,34; 22,73</t>
+          <t>12,24; 22,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 20,53</t>
+          <t>10,6; 20,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,43; 40,23</t>
+          <t>8,25; 17,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,39; 40,46</t>
+          <t>15,11; 40,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,59; 59,49</t>
+          <t>27,47; 59,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,1; 45,29</t>
+          <t>20,67; 44,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,83; 285,23</t>
+          <t>19,82; 51,37</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,93</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,68; 20,45</t>
+          <t>15,47; 20,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,36; 22,03</t>
+          <t>17,44; 22,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,31</t>
+          <t>12,6; 17,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,03; 29,34</t>
+          <t>8,73; 13,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,4; 52,31</t>
+          <t>37,26; 52,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,5; 45,08</t>
+          <t>33,54; 44,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,34; 35,68</t>
+          <t>24,46; 35,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20,5; 75,12</t>
+          <t>16,25; 26,76</t>
         </is>
       </c>
     </row>
